--- a/data/trans_dic/P1804_2016_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1804_2016_2023-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,94</t>
+          <t>6,96; 11,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,15</t>
+          <t>3,96; 7,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 13,85</t>
+          <t>9,73; 14,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 9,78</t>
+          <t>7,16; 10,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,18</t>
+          <t>8,97; 12,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,61</t>
+          <t>6,28; 8,5</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,3</t>
+          <t>4,37; 6,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,72</t>
+          <t>4,36; 6,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,65</t>
+          <t>7,14; 9,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,47</t>
+          <t>6,36; 8,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,57</t>
+          <t>5,97; 7,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,2</t>
+          <t>5,64; 7,28</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,86</t>
+          <t>4,91; 9,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,88</t>
+          <t>7,23; 12,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 15,5</t>
+          <t>9,48; 15,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,69</t>
+          <t>9,84; 14,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,95</t>
+          <t>8,11; 11,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,05</t>
+          <t>8,94; 12,38</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,18</t>
+          <t>5,51; 7,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,51</t>
+          <t>5,36; 7,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 10,98</t>
+          <t>8,91; 11,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,63</t>
+          <t>7,76; 9,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 8,82</t>
+          <t>7,5; 8,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 7,31</t>
+          <t>6,81; 8,08</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31474</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>69261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94601</t>
+          <t>101502</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51325; 82542</t>
+          <t>52493; 83766</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22605; 41987</t>
+          <t>22937; 43776</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96235; 137712</t>
+          <t>96805; 142384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53067; 73870</t>
+          <t>58778; 83919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>156892; 213001</t>
+          <t>156892; 211563</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79983; 109347</t>
+          <t>87893; 119017</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>100630</t>
+          <t>119779</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137188</t>
+          <t>160611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>237818</t>
+          <t>280390</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90088; 130769</t>
+          <t>90710; 130645</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72241; 131081</t>
+          <t>97211; 148859</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142538; 191933</t>
+          <t>141969; 193034</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96886; 166964</t>
+          <t>137638; 187142</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>244005; 307883</t>
+          <t>242640; 308481</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>189724; 280610</t>
+          <t>248036; 320026</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75828</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>134558</t>
+          <t>153841</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27398; 53947</t>
+          <t>26850; 49961</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45870; 76839</t>
+          <t>51431; 88623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52625; 85141</t>
+          <t>52078; 84979</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62634; 90449</t>
+          <t>72315; 103412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88516; 131023</t>
+          <t>88848; 128682</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>112143; 157441</t>
+          <t>129351; 179083</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276144</t>
+          <t>317166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>466978</t>
+          <t>535733</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186671; 242537</t>
+          <t>186079; 240882</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>152204; 224556</t>
+          <t>188856; 255424</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312726; 387905</t>
+          <t>314788; 392475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>228044; 314905</t>
+          <t>288762; 351620</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>517507; 609393</t>
+          <t>518026; 611075</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>398721; 519274</t>
+          <t>493441; 585210</t>
         </is>
       </c>
     </row>
